--- a/artfynd/A 55604-2025 artfynd.xlsx
+++ b/artfynd/A 55604-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130156894</v>
+        <v>130156461</v>
       </c>
       <c r="B2" t="n">
-        <v>105897</v>
+        <v>98831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568805</v>
+        <v>568776</v>
       </c>
       <c r="R2" t="n">
-        <v>6394649</v>
+        <v>6394702</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130156461</v>
+        <v>130156128</v>
       </c>
       <c r="B3" t="n">
         <v>98831</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568776</v>
+        <v>568888</v>
       </c>
       <c r="R3" t="n">
-        <v>6394702</v>
+        <v>6394715</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130156128</v>
+        <v>130156894</v>
       </c>
       <c r="B4" t="n">
-        <v>98831</v>
+        <v>105897</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568888</v>
+        <v>568805</v>
       </c>
       <c r="R4" t="n">
-        <v>6394715</v>
+        <v>6394649</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 55604-2025 artfynd.xlsx
+++ b/artfynd/A 55604-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130156461</v>
+        <v>130156894</v>
       </c>
       <c r="B2" t="n">
-        <v>98831</v>
+        <v>105897</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568776</v>
+        <v>568805</v>
       </c>
       <c r="R2" t="n">
-        <v>6394702</v>
+        <v>6394649</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130156128</v>
+        <v>130156461</v>
       </c>
       <c r="B3" t="n">
         <v>98831</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568888</v>
+        <v>568776</v>
       </c>
       <c r="R3" t="n">
-        <v>6394715</v>
+        <v>6394702</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130156894</v>
+        <v>130156128</v>
       </c>
       <c r="B4" t="n">
-        <v>105897</v>
+        <v>98831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568805</v>
+        <v>568888</v>
       </c>
       <c r="R4" t="n">
-        <v>6394649</v>
+        <v>6394715</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 55604-2025 artfynd.xlsx
+++ b/artfynd/A 55604-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130156894</v>
+        <v>130156461</v>
       </c>
       <c r="B2" t="n">
-        <v>105897</v>
+        <v>98833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568805</v>
+        <v>568776</v>
       </c>
       <c r="R2" t="n">
-        <v>6394649</v>
+        <v>6394702</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130156461</v>
+        <v>130156128</v>
       </c>
       <c r="B3" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568776</v>
+        <v>568888</v>
       </c>
       <c r="R3" t="n">
-        <v>6394702</v>
+        <v>6394715</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130156128</v>
+        <v>130156894</v>
       </c>
       <c r="B4" t="n">
-        <v>98831</v>
+        <v>105900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568888</v>
+        <v>568805</v>
       </c>
       <c r="R4" t="n">
-        <v>6394715</v>
+        <v>6394649</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
         <v>130156623</v>
       </c>
       <c r="B5" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>130156799</v>
       </c>
       <c r="B6" t="n">
-        <v>105897</v>
+        <v>105900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>130156474</v>
       </c>
       <c r="B8" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>130156599</v>
       </c>
       <c r="B9" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>130156771</v>
       </c>
       <c r="B10" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>130156608</v>
       </c>
       <c r="B11" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>130156499</v>
       </c>
       <c r="B13" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>130156593</v>
       </c>
       <c r="B14" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>130156484</v>
       </c>
       <c r="B15" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>130156264</v>
       </c>
       <c r="B16" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>130156518</v>
       </c>
       <c r="B17" t="n">
-        <v>105897</v>
+        <v>105900</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>130156747</v>
       </c>
       <c r="B18" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>130156760</v>
       </c>
       <c r="B19" t="n">
-        <v>92921</v>
+        <v>92923</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,32 +2599,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130156068</v>
+        <v>130157148</v>
       </c>
       <c r="B20" t="n">
-        <v>105897</v>
+        <v>98833</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2642,13 +2642,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>568882</v>
+        <v>568650</v>
       </c>
       <c r="R20" t="n">
-        <v>6394712</v>
+        <v>6394619</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2705,32 +2705,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130157148</v>
+        <v>130156068</v>
       </c>
       <c r="B21" t="n">
-        <v>98831</v>
+        <v>105900</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,13 +2748,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>568650</v>
+        <v>568882</v>
       </c>
       <c r="R21" t="n">
-        <v>6394619</v>
+        <v>6394712</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>130156508</v>
       </c>
       <c r="B22" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 55604-2025 artfynd.xlsx
+++ b/artfynd/A 55604-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130156461</v>
+        <v>130156128</v>
       </c>
       <c r="B2" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568776</v>
+        <v>568888</v>
       </c>
       <c r="R2" t="n">
-        <v>6394702</v>
+        <v>6394715</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130156128</v>
+        <v>130156894</v>
       </c>
       <c r="B3" t="n">
-        <v>98833</v>
+        <v>105987</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568888</v>
+        <v>568805</v>
       </c>
       <c r="R3" t="n">
-        <v>6394715</v>
+        <v>6394649</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130156894</v>
+        <v>130156461</v>
       </c>
       <c r="B4" t="n">
-        <v>105900</v>
+        <v>98920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568805</v>
+        <v>568776</v>
       </c>
       <c r="R4" t="n">
-        <v>6394649</v>
+        <v>6394702</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
         <v>130156623</v>
       </c>
       <c r="B5" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>130156799</v>
       </c>
       <c r="B6" t="n">
-        <v>105900</v>
+        <v>105987</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>130156869</v>
       </c>
       <c r="B7" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>130156474</v>
       </c>
       <c r="B8" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>130156599</v>
       </c>
       <c r="B9" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>130156771</v>
       </c>
       <c r="B10" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>130156608</v>
       </c>
       <c r="B11" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>130156436</v>
       </c>
       <c r="B12" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>130156499</v>
       </c>
       <c r="B13" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>130156593</v>
       </c>
       <c r="B14" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>130156484</v>
       </c>
       <c r="B15" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>130156264</v>
       </c>
       <c r="B16" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>130156518</v>
       </c>
       <c r="B17" t="n">
-        <v>105900</v>
+        <v>105987</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>130156747</v>
       </c>
       <c r="B18" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>130156760</v>
       </c>
       <c r="B19" t="n">
-        <v>92923</v>
+        <v>93010</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>130157148</v>
       </c>
       <c r="B20" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>130156068</v>
       </c>
       <c r="B21" t="n">
-        <v>105900</v>
+        <v>105987</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>130156508</v>
       </c>
       <c r="B22" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 55604-2025 artfynd.xlsx
+++ b/artfynd/A 55604-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130156128</v>
+        <v>130156461</v>
       </c>
       <c r="B2" t="n">
         <v>98920</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568888</v>
+        <v>568776</v>
       </c>
       <c r="R2" t="n">
-        <v>6394715</v>
+        <v>6394702</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130156894</v>
+        <v>130156128</v>
       </c>
       <c r="B3" t="n">
-        <v>105987</v>
+        <v>98920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568805</v>
+        <v>568888</v>
       </c>
       <c r="R3" t="n">
-        <v>6394649</v>
+        <v>6394715</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130156461</v>
+        <v>130156894</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>105987</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568776</v>
+        <v>568805</v>
       </c>
       <c r="R4" t="n">
-        <v>6394702</v>
+        <v>6394649</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 55604-2025 artfynd.xlsx
+++ b/artfynd/A 55604-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130156461</v>
+        <v>130156128</v>
       </c>
       <c r="B2" t="n">
         <v>98920</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568776</v>
+        <v>568888</v>
       </c>
       <c r="R2" t="n">
-        <v>6394702</v>
+        <v>6394715</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130156128</v>
+        <v>130156894</v>
       </c>
       <c r="B3" t="n">
-        <v>98920</v>
+        <v>105987</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568888</v>
+        <v>568805</v>
       </c>
       <c r="R3" t="n">
-        <v>6394715</v>
+        <v>6394649</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130156894</v>
+        <v>130156461</v>
       </c>
       <c r="B4" t="n">
-        <v>105987</v>
+        <v>98920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568805</v>
+        <v>568776</v>
       </c>
       <c r="R4" t="n">
-        <v>6394649</v>
+        <v>6394702</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -2599,32 +2599,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130157148</v>
+        <v>130156068</v>
       </c>
       <c r="B20" t="n">
-        <v>98920</v>
+        <v>105987</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2642,13 +2642,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>568650</v>
+        <v>568882</v>
       </c>
       <c r="R20" t="n">
-        <v>6394619</v>
+        <v>6394712</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2705,32 +2705,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130156068</v>
+        <v>130157148</v>
       </c>
       <c r="B21" t="n">
-        <v>105987</v>
+        <v>98920</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,13 +2748,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>568882</v>
+        <v>568650</v>
       </c>
       <c r="R21" t="n">
-        <v>6394712</v>
+        <v>6394619</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 55604-2025 artfynd.xlsx
+++ b/artfynd/A 55604-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130156461</v>
+        <v>130156894</v>
       </c>
       <c r="B2" t="n">
-        <v>98920</v>
+        <v>105987</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568776</v>
+        <v>568805</v>
       </c>
       <c r="R2" t="n">
-        <v>6394702</v>
+        <v>6394649</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130156128</v>
+        <v>130156461</v>
       </c>
       <c r="B3" t="n">
         <v>98920</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568888</v>
+        <v>568776</v>
       </c>
       <c r="R3" t="n">
-        <v>6394715</v>
+        <v>6394702</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130156894</v>
+        <v>130156128</v>
       </c>
       <c r="B4" t="n">
-        <v>105987</v>
+        <v>98920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568805</v>
+        <v>568888</v>
       </c>
       <c r="R4" t="n">
-        <v>6394649</v>
+        <v>6394715</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1739,42 +1739,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130156436</v>
+        <v>130156499</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>98920</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568759</v>
+        <v>568758</v>
       </c>
       <c r="R12" t="n">
-        <v>6394703</v>
+        <v>6394693</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,17 +1820,13 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Spår efter födosök</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1849,42 +1845,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130156499</v>
+        <v>130156436</v>
       </c>
       <c r="B13" t="n">
-        <v>98920</v>
+        <v>57823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1892,10 +1888,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>568758</v>
+        <v>568759</v>
       </c>
       <c r="R13" t="n">
-        <v>6394693</v>
+        <v>6394703</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1930,13 +1926,17 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spår efter födosök</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2599,32 +2599,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130156068</v>
+        <v>130157148</v>
       </c>
       <c r="B20" t="n">
-        <v>105987</v>
+        <v>98920</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2642,13 +2642,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>568882</v>
+        <v>568650</v>
       </c>
       <c r="R20" t="n">
-        <v>6394712</v>
+        <v>6394619</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2705,32 +2705,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130157148</v>
+        <v>130156068</v>
       </c>
       <c r="B21" t="n">
-        <v>98920</v>
+        <v>105987</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,13 +2748,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>568650</v>
+        <v>568882</v>
       </c>
       <c r="R21" t="n">
-        <v>6394619</v>
+        <v>6394712</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 55604-2025 artfynd.xlsx
+++ b/artfynd/A 55604-2025 artfynd.xlsx
@@ -1739,42 +1739,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130156499</v>
+        <v>130156436</v>
       </c>
       <c r="B12" t="n">
-        <v>98920</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568758</v>
+        <v>568759</v>
       </c>
       <c r="R12" t="n">
-        <v>6394693</v>
+        <v>6394703</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,13 +1820,17 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Spår efter födosök</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1845,42 +1849,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130156436</v>
+        <v>130156499</v>
       </c>
       <c r="B13" t="n">
-        <v>57823</v>
+        <v>98920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1888,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>568759</v>
+        <v>568758</v>
       </c>
       <c r="R13" t="n">
-        <v>6394703</v>
+        <v>6394693</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1926,17 +1930,13 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Spår efter födosök</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55604-2025 artfynd.xlsx
+++ b/artfynd/A 55604-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130156894</v>
       </c>
       <c r="B2" t="n">
-        <v>105987</v>
+        <v>105990</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>130156461</v>
       </c>
       <c r="B3" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>130156128</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>130156623</v>
       </c>
       <c r="B5" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>130156799</v>
       </c>
       <c r="B6" t="n">
-        <v>105987</v>
+        <v>105990</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>130156474</v>
       </c>
       <c r="B8" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>130156599</v>
       </c>
       <c r="B9" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>130156771</v>
       </c>
       <c r="B10" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>130156608</v>
       </c>
       <c r="B11" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>130156499</v>
       </c>
       <c r="B13" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>130156593</v>
       </c>
       <c r="B14" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>130156484</v>
       </c>
       <c r="B15" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>130156264</v>
       </c>
       <c r="B16" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>130156518</v>
       </c>
       <c r="B17" t="n">
-        <v>105987</v>
+        <v>105990</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>130156747</v>
       </c>
       <c r="B18" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>130156760</v>
       </c>
       <c r="B19" t="n">
-        <v>93010</v>
+        <v>93013</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,32 +2599,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130157148</v>
+        <v>130156068</v>
       </c>
       <c r="B20" t="n">
-        <v>98920</v>
+        <v>105990</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2642,13 +2642,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>568650</v>
+        <v>568882</v>
       </c>
       <c r="R20" t="n">
-        <v>6394619</v>
+        <v>6394712</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2705,32 +2705,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130156068</v>
+        <v>130157148</v>
       </c>
       <c r="B21" t="n">
-        <v>105987</v>
+        <v>98923</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,13 +2748,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>568882</v>
+        <v>568650</v>
       </c>
       <c r="R21" t="n">
-        <v>6394712</v>
+        <v>6394619</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>130156508</v>
       </c>
       <c r="B22" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 55604-2025 artfynd.xlsx
+++ b/artfynd/A 55604-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130156894</v>
+        <v>130156461</v>
       </c>
       <c r="B2" t="n">
-        <v>105990</v>
+        <v>98949</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568805</v>
+        <v>568776</v>
       </c>
       <c r="R2" t="n">
-        <v>6394649</v>
+        <v>6394702</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130156461</v>
+        <v>130156128</v>
       </c>
       <c r="B3" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568776</v>
+        <v>568888</v>
       </c>
       <c r="R3" t="n">
-        <v>6394702</v>
+        <v>6394715</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130156128</v>
+        <v>130156894</v>
       </c>
       <c r="B4" t="n">
-        <v>98923</v>
+        <v>106016</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568888</v>
+        <v>568805</v>
       </c>
       <c r="R4" t="n">
-        <v>6394715</v>
+        <v>6394649</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
         <v>130156623</v>
       </c>
       <c r="B5" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>130156799</v>
       </c>
       <c r="B6" t="n">
-        <v>105990</v>
+        <v>106016</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>130156869</v>
       </c>
       <c r="B7" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>130156474</v>
       </c>
       <c r="B8" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>130156599</v>
       </c>
       <c r="B9" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>130156771</v>
       </c>
       <c r="B10" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>130156608</v>
       </c>
       <c r="B11" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>130156436</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>130156499</v>
       </c>
       <c r="B13" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>130156593</v>
       </c>
       <c r="B14" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>130156484</v>
       </c>
       <c r="B15" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>130156264</v>
       </c>
       <c r="B16" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>130156518</v>
       </c>
       <c r="B17" t="n">
-        <v>105990</v>
+        <v>106016</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>130156747</v>
       </c>
       <c r="B18" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>130156760</v>
       </c>
       <c r="B19" t="n">
-        <v>93013</v>
+        <v>93039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>130156068</v>
       </c>
       <c r="B20" t="n">
-        <v>105990</v>
+        <v>106016</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>130157148</v>
       </c>
       <c r="B21" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>130156508</v>
       </c>
       <c r="B22" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 55604-2025 artfynd.xlsx
+++ b/artfynd/A 55604-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130156461</v>
       </c>
       <c r="B2" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>130156128</v>
       </c>
       <c r="B3" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>130156894</v>
       </c>
       <c r="B4" t="n">
-        <v>106016</v>
+        <v>106017</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>130156623</v>
       </c>
       <c r="B5" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>130156799</v>
       </c>
       <c r="B6" t="n">
-        <v>106016</v>
+        <v>106017</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>130156474</v>
       </c>
       <c r="B8" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>130156599</v>
       </c>
       <c r="B9" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>130156771</v>
       </c>
       <c r="B10" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>130156608</v>
       </c>
       <c r="B11" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>130156499</v>
       </c>
       <c r="B13" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>130156593</v>
       </c>
       <c r="B14" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>130156484</v>
       </c>
       <c r="B15" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>130156264</v>
       </c>
       <c r="B16" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>130156518</v>
       </c>
       <c r="B17" t="n">
-        <v>106016</v>
+        <v>106017</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>130156747</v>
       </c>
       <c r="B18" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>130156760</v>
       </c>
       <c r="B19" t="n">
-        <v>93039</v>
+        <v>93040</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,32 +2599,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130156068</v>
+        <v>130157148</v>
       </c>
       <c r="B20" t="n">
-        <v>106016</v>
+        <v>98950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2642,13 +2642,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>568882</v>
+        <v>568650</v>
       </c>
       <c r="R20" t="n">
-        <v>6394712</v>
+        <v>6394619</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2705,32 +2705,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130157148</v>
+        <v>130156068</v>
       </c>
       <c r="B21" t="n">
-        <v>98949</v>
+        <v>106017</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,13 +2748,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>568650</v>
+        <v>568882</v>
       </c>
       <c r="R21" t="n">
-        <v>6394619</v>
+        <v>6394712</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>130156508</v>
       </c>
       <c r="B22" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 55604-2025 artfynd.xlsx
+++ b/artfynd/A 55604-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130156461</v>
+        <v>130156894</v>
       </c>
       <c r="B2" t="n">
-        <v>98950</v>
+        <v>106018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568776</v>
+        <v>568805</v>
       </c>
       <c r="R2" t="n">
-        <v>6394702</v>
+        <v>6394649</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130156128</v>
+        <v>130156461</v>
       </c>
       <c r="B3" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568888</v>
+        <v>568776</v>
       </c>
       <c r="R3" t="n">
-        <v>6394715</v>
+        <v>6394702</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130156894</v>
+        <v>130156128</v>
       </c>
       <c r="B4" t="n">
-        <v>106017</v>
+        <v>98951</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568805</v>
+        <v>568888</v>
       </c>
       <c r="R4" t="n">
-        <v>6394649</v>
+        <v>6394715</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
         <v>130156623</v>
       </c>
       <c r="B5" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>130156799</v>
       </c>
       <c r="B6" t="n">
-        <v>106017</v>
+        <v>106018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>130156474</v>
       </c>
       <c r="B8" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>130156599</v>
       </c>
       <c r="B9" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>130156771</v>
       </c>
       <c r="B10" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>130156608</v>
       </c>
       <c r="B11" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>130156499</v>
       </c>
       <c r="B13" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>130156593</v>
       </c>
       <c r="B14" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>130156484</v>
       </c>
       <c r="B15" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>130156264</v>
       </c>
       <c r="B16" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>130156518</v>
       </c>
       <c r="B17" t="n">
-        <v>106017</v>
+        <v>106018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>130156747</v>
       </c>
       <c r="B18" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>130156760</v>
       </c>
       <c r="B19" t="n">
-        <v>93040</v>
+        <v>93041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,32 +2599,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130157148</v>
+        <v>130156068</v>
       </c>
       <c r="B20" t="n">
-        <v>98950</v>
+        <v>106018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2642,13 +2642,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>568650</v>
+        <v>568882</v>
       </c>
       <c r="R20" t="n">
-        <v>6394619</v>
+        <v>6394712</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2705,32 +2705,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130156068</v>
+        <v>130157148</v>
       </c>
       <c r="B21" t="n">
-        <v>106017</v>
+        <v>98951</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,13 +2748,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>568882</v>
+        <v>568650</v>
       </c>
       <c r="R21" t="n">
-        <v>6394712</v>
+        <v>6394619</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>130156508</v>
       </c>
       <c r="B22" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
